--- a/artfynd/A 28701-2024 artfynd.xlsx
+++ b/artfynd/A 28701-2024 artfynd.xlsx
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536282</v>
+        <v>119536373</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546453</v>
+        <v>546428</v>
       </c>
       <c r="R7" t="n">
-        <v>7206565</v>
+        <v>7206710</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536373</v>
+        <v>119536361</v>
       </c>
       <c r="B8" t="n">
         <v>79608</v>
@@ -1388,14 +1388,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546428</v>
+        <v>546076</v>
       </c>
       <c r="R8" t="n">
-        <v>7206710</v>
+        <v>7207717</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536361</v>
+        <v>119536389</v>
       </c>
       <c r="B9" t="n">
         <v>79608</v>
@@ -1500,14 +1500,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546076</v>
+        <v>546402</v>
       </c>
       <c r="R9" t="n">
-        <v>7207717</v>
+        <v>7206783</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536389</v>
+        <v>119536282</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546402</v>
+        <v>546453</v>
       </c>
       <c r="R10" t="n">
-        <v>7206783</v>
+        <v>7206565</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536996</v>
+        <v>119536378</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546425</v>
+        <v>546462</v>
       </c>
       <c r="R19" t="n">
-        <v>7206690</v>
+        <v>7206572</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536378</v>
+        <v>119536996</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546462</v>
+        <v>546425</v>
       </c>
       <c r="R20" t="n">
-        <v>7206572</v>
+        <v>7206690</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3831,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536688</v>
+        <v>119536972</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3843,25 +3843,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546076</v>
+        <v>546125</v>
       </c>
       <c r="R30" t="n">
-        <v>7207717</v>
+        <v>7207569</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536972</v>
+        <v>119536688</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3955,25 +3955,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546125</v>
+        <v>546076</v>
       </c>
       <c r="R31" t="n">
-        <v>7207569</v>
+        <v>7207717</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28701-2024 artfynd.xlsx
+++ b/artfynd/A 28701-2024 artfynd.xlsx
@@ -3047,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537036</v>
+        <v>119536286</v>
       </c>
       <c r="B23" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,38 +3059,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546117</v>
+        <v>546405</v>
       </c>
       <c r="R23" t="n">
-        <v>7207583</v>
+        <v>7206794</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536377</v>
+        <v>119537136</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,25 +3171,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546455</v>
+        <v>546426</v>
       </c>
       <c r="R24" t="n">
-        <v>7206644</v>
+        <v>7206741</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536286</v>
+        <v>119537036</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3283,38 +3283,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546405</v>
+        <v>546117</v>
       </c>
       <c r="R25" t="n">
-        <v>7206794</v>
+        <v>7207583</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537136</v>
+        <v>119536377</v>
       </c>
       <c r="B26" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3395,25 +3395,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546426</v>
+        <v>546455</v>
       </c>
       <c r="R26" t="n">
-        <v>7206741</v>
+        <v>7206644</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3831,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536972</v>
+        <v>119536688</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3843,25 +3843,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546125</v>
+        <v>546076</v>
       </c>
       <c r="R30" t="n">
-        <v>7207569</v>
+        <v>7207717</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536688</v>
+        <v>119536972</v>
       </c>
       <c r="B31" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3955,25 +3955,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546076</v>
+        <v>546125</v>
       </c>
       <c r="R31" t="n">
-        <v>7207717</v>
+        <v>7207569</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 28701-2024 artfynd.xlsx
+++ b/artfynd/A 28701-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119536394</v>
+        <v>119537011</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546371</v>
+        <v>546417</v>
       </c>
       <c r="R3" t="n">
-        <v>7206859</v>
+        <v>7206761</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119536048</v>
+        <v>119537013</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546418</v>
+        <v>546370</v>
       </c>
       <c r="R4" t="n">
-        <v>7206721</v>
+        <v>7206841</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537014</v>
+        <v>119537036</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546276</v>
+        <v>546117</v>
       </c>
       <c r="R5" t="n">
-        <v>7207030</v>
+        <v>7207583</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119535972</v>
+        <v>119536377</v>
       </c>
       <c r="B6" t="n">
-        <v>74638</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546112</v>
+        <v>546455</v>
       </c>
       <c r="R6" t="n">
-        <v>7207586</v>
+        <v>7206644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536373</v>
+        <v>119536971</v>
       </c>
       <c r="B7" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546428</v>
+        <v>546119</v>
       </c>
       <c r="R7" t="n">
-        <v>7206710</v>
+        <v>7207583</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536361</v>
+        <v>119537040</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546076</v>
+        <v>546427</v>
       </c>
       <c r="R8" t="n">
-        <v>7207717</v>
+        <v>7206690</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536389</v>
+        <v>119536388</v>
       </c>
       <c r="B9" t="n">
         <v>79608</v>
@@ -1504,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546402</v>
+        <v>546465</v>
       </c>
       <c r="R9" t="n">
-        <v>7206783</v>
+        <v>7206534</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536282</v>
+        <v>119537015</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546453</v>
+        <v>546247</v>
       </c>
       <c r="R10" t="n">
-        <v>7206565</v>
+        <v>7207130</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536363</v>
+        <v>119537136</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>79642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,38 +1695,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546130</v>
+        <v>546426</v>
       </c>
       <c r="R11" t="n">
-        <v>7207515</v>
+        <v>7206741</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536390</v>
+        <v>119536363</v>
       </c>
       <c r="B12" t="n">
         <v>79608</v>
@@ -1836,14 +1831,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546413</v>
+        <v>546130</v>
       </c>
       <c r="R12" t="n">
-        <v>7206776</v>
+        <v>7207515</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537012</v>
+        <v>119536286</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546404</v>
+        <v>546405</v>
       </c>
       <c r="R13" t="n">
-        <v>7206782</v>
+        <v>7206794</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536971</v>
+        <v>119536282</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,38 +2031,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546119</v>
+        <v>546453</v>
       </c>
       <c r="R14" t="n">
-        <v>7207583</v>
+        <v>7206565</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536393</v>
+        <v>119536378</v>
       </c>
       <c r="B15" t="n">
         <v>79608</v>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546368</v>
+        <v>546462</v>
       </c>
       <c r="R15" t="n">
-        <v>7206846</v>
+        <v>7206572</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536395</v>
+        <v>119537014</v>
       </c>
       <c r="B16" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546350</v>
+        <v>546276</v>
       </c>
       <c r="R16" t="n">
-        <v>7206882</v>
+        <v>7207030</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536388</v>
+        <v>119536993</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546465</v>
+        <v>546416</v>
       </c>
       <c r="R17" t="n">
-        <v>7206534</v>
+        <v>7206720</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537013</v>
+        <v>119536996</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2512,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546370</v>
+        <v>546425</v>
       </c>
       <c r="R18" t="n">
-        <v>7206841</v>
+        <v>7206690</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536378</v>
+        <v>119536802</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>90907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,38 +2591,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546462</v>
+        <v>546126</v>
       </c>
       <c r="R19" t="n">
-        <v>7206572</v>
+        <v>7207567</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,6 +2675,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2696,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536996</v>
+        <v>119536372</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2722,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2746,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546425</v>
+        <v>546426</v>
       </c>
       <c r="R20" t="n">
-        <v>7206690</v>
+        <v>7206741</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2818,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536802</v>
+        <v>119536995</v>
       </c>
       <c r="B21" t="n">
-        <v>90907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,38 +2830,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546126</v>
+        <v>546439</v>
       </c>
       <c r="R21" t="n">
-        <v>7207567</v>
+        <v>7206669</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,21 +2914,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2935,7 +2930,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536994</v>
+        <v>119536997</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2975,10 +2970,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546432</v>
+        <v>546463</v>
       </c>
       <c r="R22" t="n">
-        <v>7206714</v>
+        <v>7206576</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536286</v>
+        <v>119536361</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,38 +3054,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546405</v>
+        <v>546076</v>
       </c>
       <c r="R23" t="n">
-        <v>7206794</v>
+        <v>7207717</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3122,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119537136</v>
+        <v>119536394</v>
       </c>
       <c r="B24" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,25 +3166,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3199,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546426</v>
+        <v>546371</v>
       </c>
       <c r="R24" t="n">
-        <v>7206741</v>
+        <v>7206859</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3244,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119537036</v>
+        <v>119536393</v>
       </c>
       <c r="B25" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,34 +3282,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546117</v>
+        <v>546368</v>
       </c>
       <c r="R25" t="n">
-        <v>7207583</v>
+        <v>7206846</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536377</v>
+        <v>119535972</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3399,34 +3394,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546455</v>
+        <v>546112</v>
       </c>
       <c r="R26" t="n">
-        <v>7206644</v>
+        <v>7207586</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3458,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3468,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3495,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536375</v>
+        <v>119536688</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,38 +3502,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546440</v>
+        <v>546076</v>
       </c>
       <c r="R27" t="n">
-        <v>7206668</v>
+        <v>7207717</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3570,7 +3565,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3580,7 +3575,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3602,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536372</v>
+        <v>119536816</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,34 +3618,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546426</v>
+        <v>546126</v>
       </c>
       <c r="R28" t="n">
-        <v>7206741</v>
+        <v>7207568</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3692,7 +3687,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3719,7 +3714,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536391</v>
+        <v>119536395</v>
       </c>
       <c r="B29" t="n">
         <v>79608</v>
@@ -3759,10 +3754,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546404</v>
+        <v>546350</v>
       </c>
       <c r="R29" t="n">
-        <v>7206789</v>
+        <v>7206882</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3794,7 +3789,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3799,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536688</v>
+        <v>119536048</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3843,38 +3838,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546076</v>
+        <v>546418</v>
       </c>
       <c r="R30" t="n">
-        <v>7207717</v>
+        <v>7206721</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536972</v>
+        <v>119536373</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,34 +3959,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546125</v>
+        <v>546428</v>
       </c>
       <c r="R31" t="n">
-        <v>7207569</v>
+        <v>7206710</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536376</v>
+        <v>119536375</v>
       </c>
       <c r="B32" t="n">
         <v>79608</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546450</v>
+        <v>546440</v>
       </c>
       <c r="R32" t="n">
-        <v>7206640</v>
+        <v>7206668</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119537015</v>
+        <v>119536972</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4203,14 +4203,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546247</v>
+        <v>546125</v>
       </c>
       <c r="R33" t="n">
-        <v>7207130</v>
+        <v>7207569</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536816</v>
+        <v>119536389</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4295,34 +4295,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546126</v>
+        <v>546402</v>
       </c>
       <c r="R34" t="n">
-        <v>7207568</v>
+        <v>7206783</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,10 +4391,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119537040</v>
+        <v>119536391</v>
       </c>
       <c r="B35" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546427</v>
+        <v>546404</v>
       </c>
       <c r="R35" t="n">
-        <v>7206690</v>
+        <v>7206789</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,10 +4503,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536995</v>
+        <v>119536390</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4519,21 +4519,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546439</v>
+        <v>546413</v>
       </c>
       <c r="R36" t="n">
-        <v>7206669</v>
+        <v>7206776</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,7 +4615,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536993</v>
+        <v>119537012</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546416</v>
+        <v>546404</v>
       </c>
       <c r="R37" t="n">
-        <v>7206720</v>
+        <v>7206782</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4727,10 +4727,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536287</v>
+        <v>119536994</v>
       </c>
       <c r="B38" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4739,25 +4739,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546340</v>
+        <v>546432</v>
       </c>
       <c r="R38" t="n">
-        <v>7206905</v>
+        <v>7206714</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4951,10 +4951,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537011</v>
+        <v>119536287</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4963,25 +4963,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546417</v>
+        <v>546340</v>
       </c>
       <c r="R40" t="n">
-        <v>7206761</v>
+        <v>7206905</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5063,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537009</v>
+        <v>119536376</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546441</v>
+        <v>546450</v>
       </c>
       <c r="R41" t="n">
-        <v>7206451</v>
+        <v>7206640</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,7 +5175,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536997</v>
+        <v>119537009</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546463</v>
+        <v>546441</v>
       </c>
       <c r="R42" t="n">
-        <v>7206576</v>
+        <v>7206451</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 28701-2024 artfynd.xlsx
+++ b/artfynd/A 28701-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536388</v>
+        <v>119537015</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546465</v>
+        <v>546247</v>
       </c>
       <c r="R9" t="n">
-        <v>7206534</v>
+        <v>7207130</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537015</v>
+        <v>119536388</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546247</v>
+        <v>546465</v>
       </c>
       <c r="R10" t="n">
-        <v>7207130</v>
+        <v>7206534</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536378</v>
+        <v>119537014</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546462</v>
+        <v>546276</v>
       </c>
       <c r="R15" t="n">
-        <v>7206572</v>
+        <v>7207030</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537014</v>
+        <v>119536378</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546276</v>
+        <v>546462</v>
       </c>
       <c r="R16" t="n">
-        <v>7207030</v>
+        <v>7206572</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3714,10 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536395</v>
+        <v>119536048</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,34 +3730,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546350</v>
+        <v>546418</v>
       </c>
       <c r="R29" t="n">
-        <v>7206882</v>
+        <v>7206721</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3789,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,10 +3831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536048</v>
+        <v>119536395</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3842,39 +3847,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546418</v>
+        <v>546350</v>
       </c>
       <c r="R30" t="n">
-        <v>7206721</v>
+        <v>7206882</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5063,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536376</v>
+        <v>119537009</v>
       </c>
       <c r="B41" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546450</v>
+        <v>546441</v>
       </c>
       <c r="R41" t="n">
-        <v>7206640</v>
+        <v>7206451</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119537009</v>
+        <v>119536376</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546441</v>
+        <v>546450</v>
       </c>
       <c r="R42" t="n">
-        <v>7206451</v>
+        <v>7206640</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 28701-2024 artfynd.xlsx
+++ b/artfynd/A 28701-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119537011</v>
+        <v>119537009</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546417</v>
+        <v>546441</v>
       </c>
       <c r="R3" t="n">
-        <v>7206761</v>
+        <v>7206451</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119537013</v>
+        <v>119537011</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546370</v>
+        <v>546417</v>
       </c>
       <c r="R4" t="n">
-        <v>7206841</v>
+        <v>7206761</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537036</v>
+        <v>119536688</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>79643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546117</v>
+        <v>546076</v>
       </c>
       <c r="R5" t="n">
-        <v>7207583</v>
+        <v>7207717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536377</v>
+        <v>119537040</v>
       </c>
       <c r="B6" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546455</v>
+        <v>546427</v>
       </c>
       <c r="R6" t="n">
-        <v>7206644</v>
+        <v>7206690</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536971</v>
+        <v>119536388</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546119</v>
+        <v>546465</v>
       </c>
       <c r="R7" t="n">
-        <v>7207583</v>
+        <v>7206534</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537040</v>
+        <v>119536971</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,34 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546427</v>
+        <v>546119</v>
       </c>
       <c r="R8" t="n">
-        <v>7206690</v>
+        <v>7207583</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537015</v>
+        <v>119536282</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546247</v>
+        <v>546453</v>
       </c>
       <c r="R9" t="n">
-        <v>7207130</v>
+        <v>7206565</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536388</v>
+        <v>119536048</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546465</v>
+        <v>546418</v>
       </c>
       <c r="R10" t="n">
-        <v>7206534</v>
+        <v>7206721</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537136</v>
+        <v>119536363</v>
       </c>
       <c r="B11" t="n">
-        <v>79642</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,38 +1700,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546426</v>
+        <v>546130</v>
       </c>
       <c r="R11" t="n">
-        <v>7206741</v>
+        <v>7207515</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536363</v>
+        <v>119536996</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,34 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546130</v>
+        <v>546425</v>
       </c>
       <c r="R12" t="n">
-        <v>7207515</v>
+        <v>7206690</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536286</v>
+        <v>119537010</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1924,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546405</v>
+        <v>546468</v>
       </c>
       <c r="R13" t="n">
-        <v>7206794</v>
+        <v>7206480</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536282</v>
+        <v>119537015</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546453</v>
+        <v>546247</v>
       </c>
       <c r="R14" t="n">
-        <v>7206565</v>
+        <v>7207130</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537014</v>
+        <v>119536376</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546276</v>
+        <v>546450</v>
       </c>
       <c r="R15" t="n">
-        <v>7207030</v>
+        <v>7206640</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536378</v>
+        <v>119536361</v>
       </c>
       <c r="B16" t="n">
         <v>79608</v>
@@ -2279,14 +2284,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546462</v>
+        <v>546076</v>
       </c>
       <c r="R16" t="n">
-        <v>7206572</v>
+        <v>7207717</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536993</v>
+        <v>119536390</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546416</v>
+        <v>546413</v>
       </c>
       <c r="R17" t="n">
-        <v>7206720</v>
+        <v>7206776</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536996</v>
+        <v>119536373</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546425</v>
+        <v>546428</v>
       </c>
       <c r="R18" t="n">
-        <v>7206690</v>
+        <v>7206710</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2706,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536372</v>
+        <v>119536816</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,34 +2727,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546426</v>
+        <v>546126</v>
       </c>
       <c r="R20" t="n">
-        <v>7206741</v>
+        <v>7207568</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,10 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536997</v>
+        <v>119536391</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,21 +2951,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546463</v>
+        <v>546404</v>
       </c>
       <c r="R22" t="n">
-        <v>7206576</v>
+        <v>7206789</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3047,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536361</v>
+        <v>119536287</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,38 +3059,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546076</v>
+        <v>546340</v>
       </c>
       <c r="R23" t="n">
-        <v>7207717</v>
+        <v>7206905</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3159,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536394</v>
+        <v>119536372</v>
       </c>
       <c r="B24" t="n">
         <v>79608</v>
@@ -3194,10 +3199,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546371</v>
+        <v>546426</v>
       </c>
       <c r="R24" t="n">
-        <v>7206859</v>
+        <v>7206741</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3234,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,7 +3271,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536393</v>
+        <v>119536394</v>
       </c>
       <c r="B25" t="n">
         <v>79608</v>
@@ -3306,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546368</v>
+        <v>546371</v>
       </c>
       <c r="R25" t="n">
-        <v>7206846</v>
+        <v>7206859</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3341,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,10 +3383,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119535972</v>
+        <v>119536972</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,21 +3399,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3418,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546112</v>
+        <v>546125</v>
       </c>
       <c r="R26" t="n">
-        <v>7207586</v>
+        <v>7207569</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3453,7 +3458,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3468,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,10 +3495,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536688</v>
+        <v>119536378</v>
       </c>
       <c r="B27" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,38 +3507,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546076</v>
+        <v>546462</v>
       </c>
       <c r="R27" t="n">
-        <v>7207717</v>
+        <v>7206572</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3565,7 +3570,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3575,7 +3580,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,10 +3607,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536816</v>
+        <v>119536993</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3618,34 +3623,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546126</v>
+        <v>546416</v>
       </c>
       <c r="R28" t="n">
-        <v>7207568</v>
+        <v>7206720</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3692,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536048</v>
+        <v>119537013</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,39 +3735,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546418</v>
+        <v>546370</v>
       </c>
       <c r="R29" t="n">
-        <v>7206721</v>
+        <v>7206841</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3831,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536395</v>
+        <v>119536393</v>
       </c>
       <c r="B30" t="n">
         <v>79608</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546350</v>
+        <v>546368</v>
       </c>
       <c r="R30" t="n">
-        <v>7206882</v>
+        <v>7206846</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536373</v>
+        <v>119536994</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,21 +3959,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546428</v>
+        <v>546432</v>
       </c>
       <c r="R31" t="n">
-        <v>7206710</v>
+        <v>7206714</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536375</v>
+        <v>119537036</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>82305</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,34 +4071,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546440</v>
+        <v>546117</v>
       </c>
       <c r="R32" t="n">
-        <v>7206668</v>
+        <v>7207583</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536972</v>
+        <v>119536377</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+          <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546125</v>
+        <v>546455</v>
       </c>
       <c r="R33" t="n">
-        <v>7207569</v>
+        <v>7206644</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536389</v>
+        <v>119537014</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4295,21 +4295,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546402</v>
+        <v>546276</v>
       </c>
       <c r="R34" t="n">
-        <v>7206783</v>
+        <v>7207030</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,7 +4391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536391</v>
+        <v>119536375</v>
       </c>
       <c r="B35" t="n">
         <v>79608</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546404</v>
+        <v>546440</v>
       </c>
       <c r="R35" t="n">
-        <v>7206789</v>
+        <v>7206668</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4503,10 +4503,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536390</v>
+        <v>119536286</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,25 +4515,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546413</v>
+        <v>546405</v>
       </c>
       <c r="R36" t="n">
-        <v>7206776</v>
+        <v>7206794</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,10 +4615,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537012</v>
+        <v>119537136</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4627,20 +4627,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546404</v>
+        <v>546426</v>
       </c>
       <c r="R37" t="n">
-        <v>7206782</v>
+        <v>7206741</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4727,10 +4727,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536994</v>
+        <v>119535972</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4743,34 +4743,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Luspberget, Fatsjöluspen, Ås lm</t>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546432</v>
+        <v>546112</v>
       </c>
       <c r="R38" t="n">
-        <v>7206714</v>
+        <v>7207586</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4839,7 +4839,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537010</v>
+        <v>119536997</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546468</v>
+        <v>546463</v>
       </c>
       <c r="R39" t="n">
-        <v>7206480</v>
+        <v>7206576</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4951,10 +4951,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536287</v>
+        <v>119536389</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4963,25 +4963,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546340</v>
+        <v>546402</v>
       </c>
       <c r="R40" t="n">
-        <v>7206905</v>
+        <v>7206783</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5063,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537009</v>
+        <v>119536395</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546441</v>
+        <v>546350</v>
       </c>
       <c r="R41" t="n">
-        <v>7206451</v>
+        <v>7206882</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536376</v>
+        <v>119537012</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546450</v>
+        <v>546404</v>
       </c>
       <c r="R42" t="n">
-        <v>7206640</v>
+        <v>7206782</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
